--- a/data/trans_orig/IP16A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24633</t>
+          <t>24405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>38735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48523</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>68169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47567</t>
+          <t>47563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60745</t>
+          <t>60981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>48934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63036</t>
+          <t>63264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99441</t>
+          <t>100207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119853</t>
+          <t>119438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>21990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18693</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>31049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22613</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27308</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49774</t>
+          <t>49181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>67521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>87309</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112185</t>
+          <t>113601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75467</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93419</t>
+          <t>94012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156313</t>
+          <t>154897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180892</t>
+          <t>181189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>23832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23928</t>
+          <t>24543</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>35815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60648</t>
+          <t>60987</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43797</t>
+          <t>43166</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61045</t>
+          <t>61633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92326</t>
+          <t>91360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117483</t>
+          <t>116417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>55268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73850</t>
+          <t>72922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>62992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80828</t>
+          <t>81459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123397</t>
+          <t>124463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148554</t>
+          <t>149520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22903</t>
+          <t>23085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36116</t>
+          <t>36245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51615</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66800</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,12%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67876</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89891</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64620</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86300</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138008</t>
+          <t>138640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171072</t>
+          <t>172841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97746</t>
+          <t>96957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119761</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>105656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128090</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209275</t>
+          <t>207506</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>241707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>23486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>47772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>40433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>61524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83863</t>
+          <t>83031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58023</t>
+          <t>58138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73398</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>56519</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72166</t>
+          <t>71685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118999</t>
+          <t>119831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140814</t>
+          <t>141338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40223</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25760</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>50494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53571</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>63534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>103391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132584</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89534</t>
+          <t>89902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>110230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83572</t>
+          <t>83851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>102550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178061</t>
+          <t>178693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206485</t>
+          <t>207254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63840</t>
+          <t>63399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39655</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63058</t>
+          <t>64157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112392</t>
+          <t>113482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57003</t>
+          <t>57444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100454</t>
+          <t>97092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61117</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80369</t>
+          <t>80583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128475</t>
+          <t>127385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177809</t>
+          <t>176710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26010</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53662</t>
+          <t>52893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>51794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>89860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68245</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92357</t>
+          <t>91778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116988</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172684</t>
+          <t>171925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>87855</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134490</t>
+          <t>133859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>115070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187232</t>
+          <t>187991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242928</t>
+          <t>246380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9338</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5719</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13091</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7644</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4358</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11752</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11297</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>19,07%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>51,24%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>16981</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>12323</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>22548</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>40,14%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>53,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9338</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13171</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>29,07%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>65,02%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>16981</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>12058</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>22522</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>40,14%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -836,107 +836,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10920</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7167</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14539</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14404</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10296</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10751</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17844</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>65,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>48,76%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>80,93%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>25324</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>19757</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>29982</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>59,86%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>46,7%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10920</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7087</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14368</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>25324</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>19783</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>30247</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>59,86%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>46,76%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31968</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25280</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39878</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>26353</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19726</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33144</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20857</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33938</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>32,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31968</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24405</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>38735</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48938</t>
+          <t>49180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68169</t>
+          <t>68779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55701</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47791</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62389</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>54354</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47563</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>60981</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>46769</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>59850</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>67,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>55701</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48934</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>63264</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>63,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100207</t>
+          <t>99597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119438</t>
+          <t>119196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17311</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12661</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22665</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7299</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4239</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11421</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10831</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17311</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12589</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21990</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,09%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31049</t>
+          <t>30957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,54%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17955</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22605</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15252</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11130</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18312</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11720</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18441</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17955</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13276</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>22677</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>26859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58617</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68803</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>41295</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33713</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51225</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32833</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50167</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>58617</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>49181</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>67521</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>40,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87309</t>
+          <t>87112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113601</t>
+          <t>111390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84576</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74390</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>93445</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>84010</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74080</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91592</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>75138</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92472</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>84576</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75672</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>94012</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>59,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154897</t>
+          <t>157108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>181189</t>
+          <t>181386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8772</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5508</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12832</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9786</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6077</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13705</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5597</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13793</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>38,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8772</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5255</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12622</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>13178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>24319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14080</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10020</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17344</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15737</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11818</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19446</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11730</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19926</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>61,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14080</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10230</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17597</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>61,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24543</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>35197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52294</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43793</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61102</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43333</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60987</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>43323</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61197</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>44,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>37,27%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>52294</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>43166</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>61633</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>34,64%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91360</t>
+          <t>92517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116417</t>
+          <t>117276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72331</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63523</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80832</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64462</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>55268</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72922</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>55058</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72932</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>55,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>47,36%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>62,73%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>72331</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>62992</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>81459</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>58,04%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>50,54%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>65,36%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>198</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124463</t>
+          <t>123604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149520</t>
+          <t>148363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>124625</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>124625</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>124625</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>116255</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>116255</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>116255</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>124625</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>124625</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>124625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14132</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9561</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>17132</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12021</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22774</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12563</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23641</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14132</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8987</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19799</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39195</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31100</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24260</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35671</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>28727</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23085</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33838</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22218</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>33296</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>62,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31100</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25433</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36245</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>68,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51896</t>
+          <t>52355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66610</t>
+          <t>67892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64263</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>86818</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>78711</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>67251</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>90680</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>66003</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>88793</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>75199</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>64064</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>87054</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138640</t>
+          <t>137731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172841</t>
+          <t>170864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>117511</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>105892</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>128447</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>108926</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>96957</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>120386</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>98844</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>121634</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>58,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>117511</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>105656</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>128646</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207506</t>
+          <t>209483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241707</t>
+          <t>242616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>187637</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>187637</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>187637</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8648</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6705</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3794</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10678</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3839</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10284</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5565</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2647</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8491</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17201</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7210</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10015</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12151</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8178</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15062</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8572</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15017</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>64,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7210</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4284</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10128</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>56,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23486</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32587</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25611</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40601</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>39674</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>32361</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47772</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>32645</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48125</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32587</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>25267</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40433</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61524</t>
+          <t>62376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83031</t>
+          <t>84116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64365</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56351</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>71341</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>66236</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58138</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73549</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57785</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>73265</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>64365</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>56519</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>71685</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119831</t>
+          <t>118746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141338</t>
+          <t>140486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96952</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96952</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96952</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96952</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96952</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21340</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16793</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11922</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21945</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12180</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21823</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>43,63%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16000</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11397</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21157</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25659</t>
+          <t>25749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>21659</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16319</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26342</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>21701</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16549</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26572</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16671</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26314</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>56,37%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21659</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>16502</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26262</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36132</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>50404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>38494</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>38494</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>38494</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45123</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65094</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>63172</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>53029</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73357</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>54080</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>73578</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54153</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44835</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>63534</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>104113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131952</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93232</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>82291</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>102262</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>100087</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>89902</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>110230</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>89681</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>109179</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>93232</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>83851</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102550</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178693</t>
+          <t>179462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207254</t>
+          <t>206532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163259</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163259</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163259</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6816</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3381</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9635</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,29%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>69,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7991</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10539</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7239</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14576</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20029</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42823</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34458</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52220</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>46876</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23751</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>63399</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48536</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39441</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>53860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>95412</t>
+          <t>88960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64157</t>
+          <t>77344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113482</t>
+          <t>101003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65089</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55692</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>73454</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>73967</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57444</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>97092</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>61,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>71488</t>
+          <t>46547</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61939</t>
+          <t>38824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80583</t>
+          <t>54655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>145455</t>
+          <t>111636</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127385</t>
+          <t>99593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176710</t>
+          <t>123252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22903</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16478</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28793</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>66,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20748</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15572</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26154</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24586</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17756</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45334</t>
+          <t>42764</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>34493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52893</t>
+          <t>50124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,92%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20216</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14326</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26641</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20894</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15488</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26070</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50,17%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>42819</t>
+          <t>40883</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>61711</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>84667</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43856</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>89860</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91778</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113536</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171925</t>
+          <t>156954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92410</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80285</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103241</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>56,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>62,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>106198</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>87855</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>133859</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>102105</t>
+          <t>73348</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90423</t>
+          <t>62988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115070</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>208303</t>
+          <t>165758</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187991</t>
+          <t>150990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>246380</t>
+          <t>179703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
